--- a/filer/24257703_fcn.xlsx
+++ b/filer/24257703_fcn.xlsx
@@ -615,7 +615,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-mellem · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/24257703_fcn.xlsx
+++ b/filer/24257703_fcn.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_24257703" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_24257703" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_24257703" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_24257703" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -192,9 +193,9 @@
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -595,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -629,7 +630,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -644,35 +645,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1498,35 +1499,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -2688,35 +2689,35 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
@@ -3974,19 +3975,19 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1">
@@ -4092,19 +4093,19 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
@@ -4401,6 +4402,148 @@
       </c>
       <c r="F91" s="13">
         <f>IFERROR($F$30/($F$55+$F$60)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B94" s="17">
+        <f>'pengestrom_raw_24257703'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C94" s="17">
+        <f>'pengestrom_raw_24257703'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D94" s="17">
+        <f>'pengestrom_raw_24257703'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E94" s="17">
+        <f>'pengestrom_raw_24257703'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F94" s="17">
+        <f>'pengestrom_raw_24257703'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B95" s="17">
+        <f>'pengestrom_raw_24257703'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C95" s="17">
+        <f>'pengestrom_raw_24257703'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D95" s="17">
+        <f>'pengestrom_raw_24257703'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E95" s="17">
+        <f>'pengestrom_raw_24257703'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F95" s="17">
+        <f>'pengestrom_raw_24257703'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B96" s="17">
+        <f>'pengestrom_raw_24257703'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C96" s="17">
+        <f>'pengestrom_raw_24257703'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D96" s="17">
+        <f>'pengestrom_raw_24257703'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E96" s="17">
+        <f>'pengestrom_raw_24257703'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F96" s="17">
+        <f>'pengestrom_raw_24257703'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B97" s="17">
+        <f>'pengestrom_raw_24257703'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C97" s="17">
+        <f>'pengestrom_raw_24257703'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D97" s="17">
+        <f>'pengestrom_raw_24257703'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E97" s="17">
+        <f>'pengestrom_raw_24257703'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F97" s="17">
+        <f>'pengestrom_raw_24257703'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B98">
+        <f>IF(ABS(('pengestrom_raw_24257703'!$B$2+'pengestrom_raw_24257703'!$B$3+'pengestrom_raw_24257703'!$B$4)-'pengestrom_raw_24257703'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_24257703'!$B$2+'pengestrom_raw_24257703'!$B$3+'pengestrom_raw_24257703'!$B$4)-'pengestrom_raw_24257703'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C98">
+        <f>IF(ABS(('pengestrom_raw_24257703'!$C$2+'pengestrom_raw_24257703'!$C$3+'pengestrom_raw_24257703'!$C$4)-'pengestrom_raw_24257703'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_24257703'!$C$2+'pengestrom_raw_24257703'!$C$3+'pengestrom_raw_24257703'!$C$4)-'pengestrom_raw_24257703'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D98">
+        <f>IF(ABS(('pengestrom_raw_24257703'!$D$2+'pengestrom_raw_24257703'!$D$3+'pengestrom_raw_24257703'!$D$4)-'pengestrom_raw_24257703'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_24257703'!$D$2+'pengestrom_raw_24257703'!$D$3+'pengestrom_raw_24257703'!$D$4)-'pengestrom_raw_24257703'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E98">
+        <f>IF(ABS(('pengestrom_raw_24257703'!$E$2+'pengestrom_raw_24257703'!$E$3+'pengestrom_raw_24257703'!$E$4)-'pengestrom_raw_24257703'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_24257703'!$E$2+'pengestrom_raw_24257703'!$E$3+'pengestrom_raw_24257703'!$E$4)-'pengestrom_raw_24257703'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F98">
+        <f>IF(ABS(('pengestrom_raw_24257703'!$F$2+'pengestrom_raw_24257703'!$F$3+'pengestrom_raw_24257703'!$F$4)-'pengestrom_raw_24257703'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_24257703'!$F$2+'pengestrom_raw_24257703'!$F$3+'pengestrom_raw_24257703'!$F$4)-'pengestrom_raw_24257703'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4433,382 +4576,378 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>192257</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>215055</v>
       </c>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="16" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>-140330</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>-49233</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>-258940</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>-147989</v>
       </c>
+      <c r="F3" s="17" t="n">
+        <v>-355260</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Vareforbrug</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>82223</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>59861</v>
       </c>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Andre eksterne omkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>20458</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>28637</v>
       </c>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="16" t="n"/>
-      <c r="F5" s="16" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>89576</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>126557</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>63068</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>292394</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>366004</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>460800</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Personaleomkostninger</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>66581</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>86407</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>107976</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>178658</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>175027</v>
       </c>
+      <c r="F7" s="17" t="n">
+        <v>142050</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Resultat før afskrivninger</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Af- og nedskrivninger</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>9491</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>6670</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>15125</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>31803</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>45144</v>
       </c>
+      <c r="F9" s="17" t="n">
+        <v>35721</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>13503</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>33480</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>-60033</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>81933</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>145833</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>283029</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>652</v>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>4748</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>3132</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>1196</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>1632</v>
       </c>
+      <c r="F13" s="17" t="n">
+        <v>1590</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>1276</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>3872</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>1801</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>5840</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>5376</v>
       </c>
+      <c r="F14" s="17" t="n">
+        <v>11507</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>624</v>
-      </c>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>-1935</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>-2352</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>3551</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>2576</v>
       </c>
+      <c r="F15" s="17" t="n">
+        <v>-8779</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>12879</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>35415</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>-57681</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>78382</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>143256</v>
       </c>
+      <c r="F16" s="17" t="n">
+        <v>274250</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>2805</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>7829</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>-12518</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>17268</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>31778</v>
       </c>
+      <c r="F17" s="17" t="n">
+        <v>65011</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>10074</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>27586</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>-45163</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>61114</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>111478</v>
       </c>
+      <c r="F18" s="17" t="n">
+        <v>209239</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>114</v>
-      </c>
-      <c r="C19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>143</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>170</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>192</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>202</v>
       </c>
+      <c r="F19" s="17" t="n">
+        <v>188</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>719</v>
-      </c>
-      <c r="C20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>7964</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>13623</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>442</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>0</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>3876</v>
       </c>
     </row>
   </sheetData>
@@ -4840,923 +4979,927 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>12857</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>8733</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>28870</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>60948</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>37488</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>59944</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>5284</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>11609</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>20213</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>12434</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>1750</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>3306</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
-        <v>5284</v>
-      </c>
-      <c r="C8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>11609</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>20213</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>12434</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>1750</v>
       </c>
+      <c r="F8" s="17" t="n">
+        <v>3306</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>18141</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>20342</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>49083</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>73382</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>39238</v>
       </c>
+      <c r="F9" s="17" t="n">
+        <v>63250</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Råvarer og hjælpematerialer</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Varer under fremstilling</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="17" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Færdigvarer og handelsvarer</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
-        <v>584</v>
-      </c>
-      <c r="C12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>662</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>835</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>1429</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>1614</v>
       </c>
+      <c r="F12" s="17" t="n">
+        <v>2002</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>584</v>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>662</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>835</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>1429</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>1614</v>
       </c>
+      <c r="F13" s="17" t="n">
+        <v>2002</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>120765</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>165514</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>79978</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>54184</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>266279</v>
       </c>
+      <c r="F14" s="17" t="n">
+        <v>404441</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>65500</v>
-      </c>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>71813</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>69103</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>91225</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>112654</v>
       </c>
+      <c r="F15" s="17" t="n">
+        <v>73958</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>5194</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>9458</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>7528</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>15281</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>4365</v>
       </c>
+      <c r="F16" s="17" t="n">
+        <v>13709</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>2299</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>1177</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>2317</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>4178</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>7721</v>
       </c>
+      <c r="F17" s="17" t="n">
+        <v>6751</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>443</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>432</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>12950</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>8549</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>2352</v>
       </c>
+      <c r="F18" s="17" t="n">
+        <v>1965</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="17" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
-        <v>194202</v>
-      </c>
-      <c r="C21" s="16" t="n">
+      <c r="B21" s="17" t="n">
         <v>248394</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="C21" s="17" t="n">
         <v>171874</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="D21" s="17" t="n">
         <v>173417</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>393372</v>
       </c>
+      <c r="F21" s="17" t="n">
+        <v>500824</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
-        <v>84</v>
-      </c>
-      <c r="C22" s="16" t="n">
+      <c r="B22" s="17" t="n">
         <v>91</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="C22" s="17" t="n">
         <v>91</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="D22" s="17" t="n">
         <v>91</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="E22" s="17" t="n">
         <v>132</v>
       </c>
+      <c r="F22" s="17" t="n">
+        <v>132</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
-        <v>19603</v>
-      </c>
-      <c r="C23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <v>25311</v>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>26387</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="D23" s="17" t="n">
         <v>85051</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>16943</v>
       </c>
+      <c r="F23" s="17" t="n">
+        <v>102642</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
-        <v>214472</v>
-      </c>
-      <c r="C24" s="16" t="n">
+      <c r="B24" s="17" t="n">
         <v>274457</v>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="C24" s="17" t="n">
         <v>199187</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="D24" s="17" t="n">
         <v>259988</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="E24" s="17" t="n">
         <v>412061</v>
       </c>
+      <c r="F24" s="17" t="n">
+        <v>605600</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n">
-        <v>232613</v>
-      </c>
-      <c r="C25" s="16" t="n">
+      <c r="B25" s="17" t="n">
         <v>294800</v>
       </c>
-      <c r="D25" s="16" t="n">
+      <c r="C25" s="17" t="n">
         <v>248270</v>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="D25" s="17" t="n">
         <v>333370</v>
       </c>
-      <c r="F25" s="16" t="n">
+      <c r="E25" s="17" t="n">
         <v>451299</v>
       </c>
+      <c r="F25" s="17" t="n">
+        <v>668849</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
+      <c r="B26" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="C26" s="16" t="n">
+      <c r="C26" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="D26" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="E26" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="F26" s="17" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="17" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="17" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n">
-        <v>81323</v>
-      </c>
-      <c r="C31" s="16" t="n">
+      <c r="B31" s="17" t="n">
         <v>108721</v>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="C31" s="17" t="n">
         <v>63558</v>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="D31" s="17" t="n">
         <v>124672</v>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="E31" s="17" t="n">
         <v>236150</v>
       </c>
+      <c r="F31" s="17" t="n">
+        <v>445389</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n">
-        <v>83323</v>
-      </c>
-      <c r="C32" s="16" t="n">
+      <c r="B32" s="17" t="n">
         <v>110721</v>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="C32" s="17" t="n">
         <v>65558</v>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="D32" s="17" t="n">
         <v>126672</v>
       </c>
-      <c r="F32" s="16" t="n">
+      <c r="E32" s="17" t="n">
         <v>238150</v>
       </c>
+      <c r="F32" s="17" t="n">
+        <v>447389</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="16" t="n"/>
-      <c r="F33" s="16" t="n"/>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="17" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Langfristede lån</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n">
-        <v>55000</v>
-      </c>
-      <c r="C34" s="16" t="n">
+      <c r="B34" s="17" t="n">
         <v>48125</v>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="C34" s="17" t="n">
         <v>34375</v>
       </c>
-      <c r="E34" s="16" t="n">
+      <c r="D34" s="17" t="n">
         <v>20625</v>
       </c>
-      <c r="F34" s="16" t="n">
+      <c r="E34" s="17" t="n">
         <v>6875</v>
       </c>
+      <c r="F34" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (langfristet)</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n">
-        <v>3069</v>
-      </c>
-      <c r="C36" s="16" t="n">
+      <c r="B36" s="17" t="n">
         <v>7680</v>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="C36" s="17" t="n">
         <v>7673</v>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="D36" s="17" t="n">
         <v>99</v>
       </c>
-      <c r="F36" s="16" t="n">
+      <c r="E36" s="17" t="n">
         <v>93</v>
       </c>
+      <c r="F36" s="17" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
-        <v>58069</v>
-      </c>
-      <c r="C37" s="16" t="n">
+      <c r="B37" s="17" t="n">
         <v>55824</v>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="C37" s="17" t="n">
         <v>42103</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="D37" s="17" t="n">
         <v>25804</v>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="E37" s="17" t="n">
         <v>10037</v>
       </c>
+      <c r="F37" s="17" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="17" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n"/>
-      <c r="C39" s="16" t="n">
+      <c r="B39" s="17" t="n">
         <v>7826</v>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="C39" s="17" t="n">
         <v>14701</v>
       </c>
-      <c r="E39" s="16" t="n">
+      <c r="D39" s="17" t="n">
         <v>13750</v>
       </c>
-      <c r="F39" s="16" t="n">
+      <c r="E39" s="17" t="n">
         <v>13750</v>
       </c>
+      <c r="F39" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n">
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="E40" s="16" t="n">
+      <c r="D40" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F40" s="16" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="17" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n">
-        <v>47496</v>
-      </c>
-      <c r="C42" s="16" t="n">
+      <c r="B42" s="17" t="n">
         <v>55499</v>
       </c>
-      <c r="D42" s="16" t="n">
+      <c r="C42" s="17" t="n">
         <v>72481</v>
       </c>
-      <c r="E42" s="16" t="n">
+      <c r="D42" s="17" t="n">
         <v>121074</v>
       </c>
-      <c r="F42" s="16" t="n">
+      <c r="E42" s="17" t="n">
         <v>106175</v>
       </c>
+      <c r="F42" s="17" t="n">
+        <v>70389</v>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n">
-        <v>2768</v>
-      </c>
-      <c r="C43" s="16" t="n">
+      <c r="B43" s="17" t="n">
         <v>28236</v>
       </c>
-      <c r="D43" s="16" t="n">
+      <c r="C43" s="17" t="n">
         <v>19199</v>
       </c>
-      <c r="E43" s="16" t="n">
+      <c r="D43" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="16" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n">
+        <v>236</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
+      <c r="B45" s="17" t="n"/>
+      <c r="C45" s="17" t="n"/>
+      <c r="D45" s="17" t="n"/>
+      <c r="E45" s="17" t="n"/>
+      <c r="F45" s="17" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n">
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n">
         <v>12867</v>
       </c>
-      <c r="F46" s="16" t="n">
+      <c r="E46" s="17" t="n">
         <v>25582</v>
       </c>
+      <c r="F46" s="17" t="n">
+        <v>60145</v>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n">
-        <v>40221</v>
-      </c>
-      <c r="C47" s="16" t="n">
+      <c r="B47" s="17" t="n">
         <v>30919</v>
       </c>
-      <c r="D47" s="16" t="n">
+      <c r="C47" s="17" t="n">
         <v>32351</v>
       </c>
-      <c r="E47" s="16" t="n">
+      <c r="D47" s="17" t="n">
         <v>30456</v>
       </c>
-      <c r="F47" s="16" t="n">
+      <c r="E47" s="17" t="n">
         <v>54164</v>
       </c>
+      <c r="F47" s="17" t="n">
+        <v>86865</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n">
-        <v>737</v>
-      </c>
-      <c r="C48" s="16" t="n">
+      <c r="B48" s="17" t="n">
         <v>5775</v>
       </c>
-      <c r="D48" s="16" t="n">
+      <c r="C48" s="17" t="n">
         <v>1869</v>
       </c>
-      <c r="E48" s="16" t="n">
+      <c r="D48" s="17" t="n">
         <v>2748</v>
       </c>
-      <c r="F48" s="16" t="n">
+      <c r="E48" s="17" t="n">
         <v>3441</v>
       </c>
+      <c r="F48" s="17" t="n">
+        <v>3726</v>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="17" t="inlineStr">
+      <c r="A49" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n">
-        <v>91222</v>
-      </c>
-      <c r="C49" s="16" t="n">
+      <c r="B49" s="17" t="n">
         <v>128254</v>
       </c>
-      <c r="D49" s="16" t="n">
+      <c r="C49" s="17" t="n">
         <v>140609</v>
       </c>
-      <c r="E49" s="16" t="n">
+      <c r="D49" s="17" t="n">
         <v>180895</v>
       </c>
-      <c r="F49" s="16" t="n">
+      <c r="E49" s="17" t="n">
         <v>203112</v>
       </c>
+      <c r="F49" s="17" t="n">
+        <v>221361</v>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="inlineStr">
+      <c r="A50" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B50" s="16" t="n">
-        <v>149290</v>
-      </c>
-      <c r="C50" s="16" t="n">
+      <c r="B50" s="17" t="n">
         <v>184079</v>
       </c>
-      <c r="D50" s="16" t="n">
+      <c r="C50" s="17" t="n">
         <v>182712</v>
       </c>
-      <c r="E50" s="16" t="n">
+      <c r="D50" s="17" t="n">
         <v>206698</v>
       </c>
-      <c r="F50" s="16" t="n">
+      <c r="E50" s="17" t="n">
         <v>213149</v>
       </c>
+      <c r="F50" s="17" t="n">
+        <v>221460</v>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="17" t="inlineStr">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B51" s="16" t="n">
-        <v>232613</v>
-      </c>
-      <c r="C51" s="16" t="n">
+      <c r="B51" s="17" t="n">
         <v>294800</v>
       </c>
-      <c r="D51" s="16" t="n">
+      <c r="C51" s="17" t="n">
         <v>248270</v>
       </c>
-      <c r="E51" s="16" t="n">
+      <c r="D51" s="17" t="n">
         <v>333370</v>
       </c>
-      <c r="F51" s="16" t="n">
+      <c r="E51" s="17" t="n">
         <v>451299</v>
+      </c>
+      <c r="F51" s="17" t="n">
+        <v>668849</v>
       </c>
     </row>
   </sheetData>
@@ -5765,6 +5908,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>-28</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>-67735</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>-117985</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>-176207</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>-218916</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-8870</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>80790</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>233774</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>136989</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>295527</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>17374</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>-11979</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-57125</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>-16023</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>34670</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5795,13 +6060,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -6515,7 +6780,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -6633,7 +6898,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -6809,7 +7074,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
